--- a/data/trans_orig/P6905-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P6905-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que tiene dolores de cabeza en 2007</t>
+          <t>Población según si su trabajo le afecta de manera que tiene dolores de cabeza en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11788</t>
+          <t>11650</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25732</t>
+          <t>25620</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>60,06%</t>
+          <t>59,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12412</t>
+          <t>12998</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23113</t>
+          <t>23473</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>43,37%</t>
+          <t>45,42%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>80,76%</t>
+          <t>82,02%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>27563</t>
+          <t>27954</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>45277</t>
+          <t>45805</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>38,57%</t>
+          <t>39,12%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>63,36%</t>
+          <t>64,1%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17112</t>
+          <t>17224</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>31056</t>
+          <t>31194</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>39,94%</t>
+          <t>40,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>72,49%</t>
+          <t>72,81%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5506</t>
+          <t>5146</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16207</t>
+          <t>15621</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>56,63%</t>
+          <t>54,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>26186</t>
+          <t>25658</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>43900</t>
+          <t>43509</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>36,64%</t>
+          <t>35,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>61,43%</t>
+          <t>60,88%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9865</t>
+          <t>9670</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26399</t>
+          <t>27799</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>38,4%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4577</t>
+          <t>4672</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14018</t>
+          <t>13843</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>42,88%</t>
+          <t>42,35%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>17220</t>
+          <t>17333</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>36360</t>
+          <t>36629</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,6%</t>
+          <t>34,86%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>45998</t>
+          <t>44598</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>62532</t>
+          <t>62727</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>63,54%</t>
+          <t>61,6%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,37%</t>
+          <t>86,64%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>18670</t>
+          <t>18845</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>28111</t>
+          <t>28016</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>57,12%</t>
+          <t>57,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>86,0%</t>
+          <t>85,71%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>68724</t>
+          <t>68455</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>87864</t>
+          <t>87751</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>65,4%</t>
+          <t>65,14%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,61%</t>
+          <t>83,51%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4273</t>
+          <t>4646</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15833</t>
+          <t>15599</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>43,24%</t>
+          <t>42,6%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1007</t>
+          <t>1012</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8935</t>
+          <t>8911</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>41,13%</t>
+          <t>41,02%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7756</t>
+          <t>7592</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>21972</t>
+          <t>20667</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>37,66%</t>
+          <t>35,43%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20782</t>
+          <t>21016</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>32342</t>
+          <t>31969</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>56,76%</t>
+          <t>57,4%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,33%</t>
+          <t>87,31%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>12789</t>
+          <t>12813</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>20717</t>
+          <t>20712</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>58,87%</t>
+          <t>58,98%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>36367</t>
+          <t>37672</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>50583</t>
+          <t>50747</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>62,34%</t>
+          <t>64,57%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,71%</t>
+          <t>86,99%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8716</t>
+          <t>8055</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21971</t>
+          <t>22115</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>37,67%</t>
+          <t>37,92%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3307</t>
+          <t>3399</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12433</t>
+          <t>12407</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>54,75%</t>
+          <t>54,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>14503</t>
+          <t>15280</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>31147</t>
+          <t>31696</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>38,44%</t>
+          <t>39,12%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>36352</t>
+          <t>36208</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>49607</t>
+          <t>50268</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>62,33%</t>
+          <t>62,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,06%</t>
+          <t>86,19%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>10273</t>
+          <t>10299</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>19399</t>
+          <t>19307</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>45,25%</t>
+          <t>45,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,43%</t>
+          <t>85,03%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>49882</t>
+          <t>49333</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>66526</t>
+          <t>65749</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>61,56%</t>
+          <t>60,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,1%</t>
+          <t>81,14%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1882</t>
+          <t>2409</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10299</t>
+          <t>10448</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>44,87%</t>
+          <t>45,52%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,7 +2140,7 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>983</t>
+          <t>984</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4857</t>
+          <t>4774</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14773</t>
+          <t>15093</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>49,37%</t>
+          <t>50,43%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12655</t>
+          <t>12506</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>21072</t>
+          <t>20545</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>55,13%</t>
+          <t>54,48%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91,8%</t>
+          <t>89,51%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2258,7 +2258,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5987</t>
+          <t>5986</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,89%</t>
+          <t>85,88%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>15152</t>
+          <t>14832</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>25068</t>
+          <t>25151</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>50,63%</t>
+          <t>49,57%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>83,77%</t>
+          <t>84,05%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12210</t>
+          <t>13185</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>25876</t>
+          <t>26749</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>31,53%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>61,89%</t>
+          <t>63,98%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5058</t>
+          <t>5424</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>12154</t>
+          <t>12333</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>35,89%</t>
+          <t>38,49%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>86,24%</t>
+          <t>87,5%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>20360</t>
+          <t>21411</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>36730</t>
+          <t>35734</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>36,42%</t>
+          <t>38,3%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>65,7%</t>
+          <t>63,92%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>15934</t>
+          <t>15061</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>29600</t>
+          <t>28625</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>38,11%</t>
+          <t>36,02%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>70,8%</t>
+          <t>68,47%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1940</t>
+          <t>1761</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>9036</t>
+          <t>8670</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>64,11%</t>
+          <t>61,51%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>19173</t>
+          <t>20169</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>35543</t>
+          <t>34492</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>36,08%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>63,58%</t>
+          <t>61,7%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>20610</t>
+          <t>20014</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>40378</t>
+          <t>38098</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>45,65%</t>
+          <t>43,07%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>11109</t>
+          <t>11431</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>23603</t>
+          <t>24256</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>25,52%</t>
+          <t>26,26%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>54,22%</t>
+          <t>55,72%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>36121</t>
+          <t>36191</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>57559</t>
+          <t>58428</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>27,37%</t>
+          <t>27,42%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>43,61%</t>
+          <t>44,27%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>48070</t>
+          <t>50350</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>67838</t>
+          <t>68434</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>54,35%</t>
+          <t>56,93%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>76,7%</t>
+          <t>77,37%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>19932</t>
+          <t>19279</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>32426</t>
+          <t>32104</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>45,78%</t>
+          <t>44,28%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>74,48%</t>
+          <t>73,74%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>74424</t>
+          <t>73555</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>95862</t>
+          <t>95792</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>56,39%</t>
+          <t>55,73%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>72,63%</t>
+          <t>72,58%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>20859</t>
+          <t>20306</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>38697</t>
+          <t>38070</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>35,53%</t>
+          <t>34,95%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>15131</t>
+          <t>15120</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>28723</t>
+          <t>29290</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>30,39%</t>
+          <t>30,37%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>57,69%</t>
+          <t>58,83%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>38895</t>
+          <t>38941</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>62558</t>
+          <t>62258</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>24,54%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>39,42%</t>
+          <t>39,23%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>70218</t>
+          <t>70845</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>88056</t>
+          <t>88609</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>64,47%</t>
+          <t>65,05%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>80,85%</t>
+          <t>81,36%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>21063</t>
+          <t>20496</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>34655</t>
+          <t>34666</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>42,31%</t>
+          <t>41,17%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>69,61%</t>
+          <t>69,63%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>96143</t>
+          <t>96443</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>119806</t>
+          <t>119760</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>60,58%</t>
+          <t>60,77%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>75,49%</t>
+          <t>75,46%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>120280</t>
+          <t>123771</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>163652</t>
+          <t>166150</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>26,21%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>34,65%</t>
+          <t>35,18%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>77154</t>
+          <t>76002</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>104241</t>
+          <t>104901</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>35,05%</t>
+          <t>34,53%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>47,36%</t>
+          <t>47,66%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>209046</t>
+          <t>204964</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>259159</t>
+          <t>256786</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>29,6%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>37,43%</t>
+          <t>37,08%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>308653</t>
+          <t>306155</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>352025</t>
+          <t>348534</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>65,35%</t>
+          <t>64,82%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>74,53%</t>
+          <t>73,79%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>115880</t>
+          <t>115220</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>142967</t>
+          <t>144119</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>52,64%</t>
+          <t>52,34%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>64,95%</t>
+          <t>65,47%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>433268</t>
+          <t>435641</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>483381</t>
+          <t>487463</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>62,57%</t>
+          <t>62,92%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>69,81%</t>
+          <t>70,4%</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que tiene dolores de cabeza en 2012</t>
+          <t>Población según si su trabajo le afecta de manera que tiene dolores de cabeza en 2012 (tasa de respuesta: 98,64%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12931</t>
+          <t>12928</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26092</t>
+          <t>25887</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4076,7 +4076,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>66,07%</t>
+          <t>65,55%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13857</t>
+          <t>14272</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24534</t>
+          <t>24969</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>47,53%</t>
+          <t>48,96%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>84,16%</t>
+          <t>85,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>30901</t>
+          <t>30447</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>47292</t>
+          <t>47228</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>45,02%</t>
+          <t>44,35%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>68,89%</t>
+          <t>68,8%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13402</t>
+          <t>13607</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>26563</t>
+          <t>26566</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,7 +4184,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>33,93%</t>
+          <t>34,45%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4618</t>
+          <t>4183</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15295</t>
+          <t>14880</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>52,47%</t>
+          <t>51,04%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>21354</t>
+          <t>21418</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>37745</t>
+          <t>38199</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>31,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>54,98%</t>
+          <t>55,65%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10138</t>
+          <t>10235</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23729</t>
+          <t>23900</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>41,93%</t>
+          <t>42,23%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3097</t>
+          <t>2966</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13587</t>
+          <t>12987</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>39,59%</t>
+          <t>37,85%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>15727</t>
+          <t>15460</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>33322</t>
+          <t>32651</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>36,66%</t>
+          <t>35,92%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>32861</t>
+          <t>32690</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>46452</t>
+          <t>46355</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>58,07%</t>
+          <t>57,77%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>82,08%</t>
+          <t>81,91%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>20728</t>
+          <t>21328</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>31218</t>
+          <t>31349</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>60,41%</t>
+          <t>62,15%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,98%</t>
+          <t>91,36%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>57583</t>
+          <t>58254</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>75178</t>
+          <t>75445</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>63,34%</t>
+          <t>64,08%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,7%</t>
+          <t>82,99%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2947</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12398</t>
+          <t>11760</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>51,07%</t>
+          <t>48,44%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>979</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8428</t>
+          <t>8512</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>46,99%</t>
+          <t>47,46%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5764</t>
+          <t>5854</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17075</t>
+          <t>16950</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>40,45%</t>
+          <t>40,15%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11878</t>
+          <t>12516</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>21329</t>
+          <t>21395</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>48,93%</t>
+          <t>51,56%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,86%</t>
+          <t>88,13%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9507</t>
+          <t>9423</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>16956</t>
+          <t>16869</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>53,01%</t>
+          <t>52,54%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,05%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>25137</t>
+          <t>25262</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>36448</t>
+          <t>36358</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>59,55%</t>
+          <t>59,85%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,34%</t>
+          <t>86,13%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3634</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14265</t>
+          <t>14953</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,8%</t>
+          <t>33,33%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9315</t>
+          <t>9028</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>20480</t>
+          <t>19920</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>31,54%</t>
+          <t>30,57%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>69,34%</t>
+          <t>67,44%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>15108</t>
+          <t>14956</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>30927</t>
+          <t>30630</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>41,57%</t>
+          <t>41,17%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>30595</t>
+          <t>29907</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>41226</t>
+          <t>41199</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>68,2%</t>
+          <t>66,67%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,9%</t>
+          <t>91,84%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>9055</t>
+          <t>9615</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>20220</t>
+          <t>20507</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>30,66%</t>
+          <t>32,56%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>68,46%</t>
+          <t>69,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>43468</t>
+          <t>43765</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>59287</t>
+          <t>59439</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>58,43%</t>
+          <t>58,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>79,69%</t>
+          <t>79,9%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>893</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7242</t>
+          <t>7149</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>44,79%</t>
+          <t>44,21%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3411</t>
+          <t>3542</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10624</t>
+          <t>10599</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>30,38%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>90,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6092</t>
+          <t>6116</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>16869</t>
+          <t>16466</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>60,62%</t>
+          <t>59,17%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8927</t>
+          <t>9020</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>16169</t>
+          <t>15276</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>55,21%</t>
+          <t>55,79%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>94,48%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1037</t>
+          <t>1062</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8250</t>
+          <t>8119</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>70,75%</t>
+          <t>69,62%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>10961</t>
+          <t>11364</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>21738</t>
+          <t>21714</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>39,38%</t>
+          <t>40,83%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>78,11%</t>
+          <t>78,02%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4751</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>16930</t>
+          <t>17014</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>39,03%</t>
+          <t>39,22%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>920</t>
+          <t>952</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7685</t>
+          <t>7632</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>50,61%</t>
+          <t>50,26%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>7763</t>
+          <t>7900</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>20900</t>
+          <t>20973</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>35,69%</t>
+          <t>35,81%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>26450</t>
+          <t>26366</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>38629</t>
+          <t>38302</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>60,97%</t>
+          <t>60,78%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>89,05%</t>
+          <t>88,29%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>7499</t>
+          <t>7552</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>14264</t>
+          <t>14232</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>49,39%</t>
+          <t>49,74%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>37664</t>
+          <t>37591</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>50801</t>
+          <t>50664</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>64,31%</t>
+          <t>64,19%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>86,74%</t>
+          <t>86,51%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>8752</t>
+          <t>9191</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>23361</t>
+          <t>23012</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>42,92%</t>
+          <t>42,28%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>13869</t>
+          <t>12364</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>27185</t>
+          <t>26802</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>58,61%</t>
+          <t>57,79%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>25930</t>
+          <t>26000</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>44429</t>
+          <t>45731</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>25,79%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>44,07%</t>
+          <t>45,36%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>31069</t>
+          <t>31418</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>45678</t>
+          <t>45239</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>57,08%</t>
+          <t>57,72%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>83,92%</t>
+          <t>83,11%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>19195</t>
+          <t>19578</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>32511</t>
+          <t>34016</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>41,39%</t>
+          <t>42,21%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>70,1%</t>
+          <t>73,34%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>56381</t>
+          <t>55079</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>74880</t>
+          <t>74810</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>55,93%</t>
+          <t>54,64%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>74,28%</t>
+          <t>74,21%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2884</t>
+          <t>2128</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>11998</t>
+          <t>12021</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>5498</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>17924</t>
+          <t>17963</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>58,44%</t>
+          <t>58,57%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>9962</t>
+          <t>9426</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>25847</t>
+          <t>26648</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>33,65%</t>
+          <t>34,69%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>34150</t>
+          <t>34127</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>43264</t>
+          <t>44020</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>74,0%</t>
+          <t>73,95%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>12748</t>
+          <t>12709</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>25174</t>
+          <t>25189</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>41,56%</t>
+          <t>41,43%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>82,07%</t>
+          <t>82,12%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>50973</t>
+          <t>50172</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>66858</t>
+          <t>67394</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>66,35%</t>
+          <t>65,31%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>87,03%</t>
+          <t>87,73%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>69651</t>
+          <t>69688</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>102071</t>
+          <t>100601</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>31,37%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>74043</t>
+          <t>72440</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>103828</t>
+          <t>103677</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>34,47%</t>
+          <t>33,72%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>48,33%</t>
+          <t>48,26%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>150211</t>
+          <t>152744</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>195919</t>
+          <t>193169</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>36,27%</t>
+          <t>35,76%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>223276</t>
+          <t>224746</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>255696</t>
+          <t>255659</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>68,63%</t>
+          <t>69,08%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>78,59%</t>
+          <t>78,58%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>111007</t>
+          <t>111158</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>140792</t>
+          <t>142395</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>51,67%</t>
+          <t>51,74%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>65,53%</t>
+          <t>66,28%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>344263</t>
+          <t>347013</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>389971</t>
+          <t>387438</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>63,73%</t>
+          <t>64,24%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>72,19%</t>
+          <t>71,72%</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que tiene dolores de cabeza en 2016</t>
+          <t>Población según si su trabajo le afecta de manera que tiene dolores de cabeza en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12149</t>
+          <t>12136</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28321</t>
+          <t>27969</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>48,35%</t>
+          <t>47,75%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14036</t>
+          <t>13645</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>26878</t>
+          <t>27267</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>34,33%</t>
+          <t>33,38%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>65,74%</t>
+          <t>66,69%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>29842</t>
+          <t>29421</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>50277</t>
+          <t>50366</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>29,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>50,55%</t>
+          <t>50,64%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>30256</t>
+          <t>30608</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>46428</t>
+          <t>46441</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>51,65%</t>
+          <t>52,25%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>79,26%</t>
+          <t>79,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14006</t>
+          <t>13617</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>26848</t>
+          <t>27239</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>34,26%</t>
+          <t>33,31%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>65,67%</t>
+          <t>66,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>49184</t>
+          <t>49095</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>69619</t>
+          <t>70040</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>49,45%</t>
+          <t>49,36%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>70,0%</t>
+          <t>70,42%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18750</t>
+          <t>19033</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>35884</t>
+          <t>36168</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>43,35%</t>
+          <t>43,69%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11930</t>
+          <t>12424</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24697</t>
+          <t>25063</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>57,84%</t>
+          <t>58,7%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>35004</t>
+          <t>34769</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>56616</t>
+          <t>55895</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>27,71%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>45,12%</t>
+          <t>44,54%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>46902</t>
+          <t>46618</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>64036</t>
+          <t>63753</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>56,65%</t>
+          <t>56,31%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>77,35%</t>
+          <t>77,01%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>18000</t>
+          <t>17634</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>30767</t>
+          <t>30273</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>42,16%</t>
+          <t>41,3%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>72,06%</t>
+          <t>70,9%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>68867</t>
+          <t>69588</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>90479</t>
+          <t>90714</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>54,88%</t>
+          <t>55,46%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>72,1%</t>
+          <t>72,29%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>843</t>
+          <t>824</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7150</t>
+          <t>6392</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>33,64%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8105,7 +8105,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5326</t>
+          <t>5333</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>42,61%</t>
+          <t>42,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1746</t>
+          <t>1748</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9059</t>
+          <t>9462</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>28,03%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14104</t>
+          <t>14862</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>20411</t>
+          <t>20430</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>66,36%</t>
+          <t>69,93%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,7 +8213,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7175</t>
+          <t>7168</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -8228,7 +8228,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>57,39%</t>
+          <t>57,34%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>24696</t>
+          <t>24293</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>32009</t>
+          <t>32007</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>73,16%</t>
+          <t>71,97%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>94,82%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7615</t>
+          <t>7432</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19326</t>
+          <t>19343</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>59,53%</t>
+          <t>59,58%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10145</t>
+          <t>10819</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21319</t>
+          <t>21136</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>33,89%</t>
+          <t>36,14%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>71,22%</t>
+          <t>70,61%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>21047</t>
+          <t>21564</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>37581</t>
+          <t>37640</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>33,73%</t>
+          <t>34,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>60,23%</t>
+          <t>60,32%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>13139</t>
+          <t>13122</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>24850</t>
+          <t>25033</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>40,47%</t>
+          <t>40,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>76,54%</t>
+          <t>77,11%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>8616</t>
+          <t>8799</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>19790</t>
+          <t>19116</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>28,78%</t>
+          <t>29,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>66,11%</t>
+          <t>63,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>24819</t>
+          <t>24760</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>41353</t>
+          <t>40836</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>39,77%</t>
+          <t>39,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>66,27%</t>
+          <t>65,44%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2338</t>
+          <t>2869</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10548</t>
+          <t>10719</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>70,93%</t>
+          <t>72,09%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,7 +8786,7 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1121</t>
+          <t>1109</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -8801,7 +8801,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5682</t>
+          <t>5762</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>15097</t>
+          <t>15168</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>27,92%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>73,14%</t>
+          <t>73,48%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4322</t>
+          <t>4151</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12532</t>
+          <t>12001</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>27,91%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>84,28%</t>
+          <t>80,7%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8904,7 +8904,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4650</t>
+          <t>4662</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8919,7 +8919,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>80,58%</t>
+          <t>80,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5544</t>
+          <t>5473</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>14959</t>
+          <t>14879</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>26,52%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>72,47%</t>
+          <t>72,08%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>945</t>
+          <t>935</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7269</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>32,4%</t>
+          <t>31,89%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1036</t>
+          <t>1014</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6476</t>
+          <t>6481</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>87,19%</t>
+          <t>87,26%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2400</t>
+          <t>2943</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>11743</t>
+          <t>12400</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>39,33%</t>
+          <t>41,53%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>15165</t>
+          <t>15279</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>21489</t>
+          <t>21499</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>67,6%</t>
+          <t>68,11%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>951</t>
+          <t>946</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6391</t>
+          <t>6413</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,04%</t>
+          <t>86,35%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>18117</t>
+          <t>17460</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>27460</t>
+          <t>26917</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>60,67%</t>
+          <t>58,47%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>90,14%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7518</t>
+          <t>6913</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>21044</t>
+          <t>21418</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>14028</t>
+          <t>13663</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>28664</t>
+          <t>29175</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>24,54%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>51,48%</t>
+          <t>52,4%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>24029</t>
+          <t>24745</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>44407</t>
+          <t>44766</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>33,4%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>57298</t>
+          <t>56924</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>70824</t>
+          <t>71429</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>73,14%</t>
+          <t>72,66%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>90,4%</t>
+          <t>91,18%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>27018</t>
+          <t>26507</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>41654</t>
+          <t>42019</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>48,52%</t>
+          <t>47,6%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>74,81%</t>
+          <t>75,46%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>89617</t>
+          <t>89258</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>109995</t>
+          <t>109279</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>66,87%</t>
+          <t>66,6%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>82,07%</t>
+          <t>81,54%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>5299</t>
+          <t>5130</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>16707</t>
+          <t>16426</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>42,54%</t>
+          <t>41,83%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>971</t>
+          <t>974</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>8466</t>
+          <t>8487</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>39,56%</t>
+          <t>39,66%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>8121</t>
+          <t>7998</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>21665</t>
+          <t>22272</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>35,71%</t>
+          <t>36,71%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>22567</t>
+          <t>22848</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>33975</t>
+          <t>34144</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>57,46%</t>
+          <t>58,17%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>86,51%</t>
+          <t>86,94%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>12934</t>
+          <t>12913</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>20429</t>
+          <t>20426</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>60,44%</t>
+          <t>60,34%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>39009</t>
+          <t>38402</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>52553</t>
+          <t>52676</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>64,29%</t>
+          <t>63,29%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>86,61%</t>
+          <t>86,82%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>80193</t>
+          <t>78681</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>114490</t>
+          <t>112585</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>32,71%</t>
+          <t>32,17%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>75682</t>
+          <t>74529</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>104613</t>
+          <t>104549</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>34,99%</t>
+          <t>34,46%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>48,37%</t>
+          <t>48,34%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>160012</t>
+          <t>162076</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>206249</t>
+          <t>208156</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>36,42%</t>
+          <t>36,76%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>235511</t>
+          <t>237416</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>269808</t>
+          <t>271320</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>67,29%</t>
+          <t>67,83%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>77,09%</t>
+          <t>77,52%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>111685</t>
+          <t>111749</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>140616</t>
+          <t>141769</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>51,63%</t>
+          <t>51,66%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>65,01%</t>
+          <t>65,54%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>360050</t>
+          <t>358143</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>406287</t>
+          <t>404223</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>63,58%</t>
+          <t>63,24%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>71,74%</t>
+          <t>71,38%</t>
         </is>
       </c>
     </row>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que tiene dolores de cabeza en 2023</t>
+          <t>Población según si su trabajo le afecta de manera que tiene dolores de cabeza en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4370</t>
+          <t>4916</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15474</t>
+          <t>15721</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>64,29%</t>
+          <t>65,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4453</t>
+          <t>4570</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10465</t>
+          <t>10691</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>29,01%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>66,42%</t>
+          <t>67,86%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11514</t>
+          <t>11445</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>23622</t>
+          <t>23801</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>28,74%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>59,32%</t>
+          <t>59,77%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8595</t>
+          <t>8348</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19699</t>
+          <t>19153</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>35,71%</t>
+          <t>34,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>81,84%</t>
+          <t>79,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5290</t>
+          <t>5064</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11302</t>
+          <t>11185</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>33,58%</t>
+          <t>32,14%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>71,74%</t>
+          <t>70,99%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>16202</t>
+          <t>16023</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>28310</t>
+          <t>28379</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>40,68%</t>
+          <t>40,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>71,09%</t>
+          <t>71,26%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3216</t>
+          <t>3858</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17639</t>
+          <t>19176</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>38,11%</t>
+          <t>41,43%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19685</t>
+          <t>18988</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>31146</t>
+          <t>31085</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>43,32%</t>
+          <t>41,78%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>68,54%</t>
+          <t>68,4%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>26038</t>
+          <t>26447</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>45424</t>
+          <t>45923</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>28,39%</t>
+          <t>28,83%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>49,52%</t>
+          <t>50,07%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>28641</t>
+          <t>27104</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>43064</t>
+          <t>42422</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>61,89%</t>
+          <t>58,57%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>91,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>14297</t>
+          <t>14358</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>25758</t>
+          <t>26455</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>31,6%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>56,68%</t>
+          <t>58,22%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>46299</t>
+          <t>45800</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>65685</t>
+          <t>65276</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>50,48%</t>
+          <t>49,93%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>71,61%</t>
+          <t>71,17%</t>
         </is>
       </c>
     </row>
@@ -11393,7 +11393,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5958</t>
+          <t>6694</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11408,7 +11408,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4856</t>
+          <t>5522</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13691</t>
+          <t>13969</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>30,42%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6327</t>
+          <t>6243</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17533</t>
+          <t>16729</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>17,53%</t>
         </is>
       </c>
     </row>
@@ -11501,7 +11501,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>43537</t>
+          <t>42801</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -11516,7 +11516,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>87,96%</t>
+          <t>86,48%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>32235</t>
+          <t>31957</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>41070</t>
+          <t>40404</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>70,19%</t>
+          <t>69,58%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,43%</t>
+          <t>87,98%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>77889</t>
+          <t>78693</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>89095</t>
+          <t>89179</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>81,63%</t>
+          <t>82,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>93,46%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7815</t>
+          <t>7997</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24170</t>
+          <t>24252</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>59,9%</t>
+          <t>60,1%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6629</t>
+          <t>5261</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>38566</t>
+          <t>37261</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>47,82%</t>
+          <t>46,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>15303</t>
+          <t>14819</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>55248</t>
+          <t>54041</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>45,66%</t>
+          <t>44,66%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>16183</t>
+          <t>16101</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>32538</t>
+          <t>32356</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>40,1%</t>
+          <t>39,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>80,63%</t>
+          <t>80,18%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>42086</t>
+          <t>43391</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>74023</t>
+          <t>75391</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>52,18%</t>
+          <t>53,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>93,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>65757</t>
+          <t>66964</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>105702</t>
+          <t>106186</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>54,34%</t>
+          <t>55,34%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,35%</t>
+          <t>87,75%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>677</t>
+          <t>703</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5716</t>
+          <t>5887</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>32,19%</t>
+          <t>33,16%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>383</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3990</t>
+          <t>3845</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>36,32%</t>
+          <t>35,0%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1779</t>
+          <t>1878</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7786</t>
+          <t>8132</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>28,29%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12041</t>
+          <t>11870</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17080</t>
+          <t>17054</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>67,81%</t>
+          <t>66,84%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6996</t>
+          <t>7141</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10582</t>
+          <t>10603</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>63,68%</t>
+          <t>65,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>20957</t>
+          <t>20611</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>26964</t>
+          <t>26865</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>72,91%</t>
+          <t>71,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,47%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2950</t>
+          <t>2908</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11533</t>
+          <t>11490</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>36,48%</t>
+          <t>36,34%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4234</t>
+          <t>4443</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11535</t>
+          <t>11702</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>38,18%</t>
+          <t>38,73%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>8745</t>
+          <t>9038</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>20751</t>
+          <t>19897</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>33,56%</t>
+          <t>32,18%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>20083</t>
+          <t>20126</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>28666</t>
+          <t>28708</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>63,52%</t>
+          <t>63,66%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>90,8%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>18680</t>
+          <t>18513</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>25981</t>
+          <t>25772</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>61,82%</t>
+          <t>61,27%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>85,99%</t>
+          <t>85,29%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>41080</t>
+          <t>41934</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>53086</t>
+          <t>52793</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>66,44%</t>
+          <t>67,82%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>85,86%</t>
+          <t>85,38%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>11495</t>
+          <t>11381</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>27136</t>
+          <t>26106</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>37,08%</t>
+          <t>35,68%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>21087</t>
+          <t>20936</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>35629</t>
+          <t>35590</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>29,69%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>50,52%</t>
+          <t>50,46%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>36524</t>
+          <t>37049</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>56939</t>
+          <t>57874</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>25,78%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>39,62%</t>
+          <t>40,27%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>46042</t>
+          <t>47072</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>61683</t>
+          <t>61797</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>62,92%</t>
+          <t>64,32%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>84,29%</t>
+          <t>84,45%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>34898</t>
+          <t>34937</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>49440</t>
+          <t>49591</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>49,48%</t>
+          <t>49,54%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>70,1%</t>
+          <t>70,31%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>86766</t>
+          <t>85831</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>107181</t>
+          <t>106656</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>60,38%</t>
+          <t>59,73%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>74,58%</t>
+          <t>74,22%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>7935</t>
+          <t>8322</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>21547</t>
+          <t>21962</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>37,96%</t>
+          <t>38,69%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>8433</t>
+          <t>8479</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>27541</t>
+          <t>28199</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>50,34%</t>
+          <t>51,54%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>19879</t>
+          <t>20114</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>43654</t>
+          <t>43110</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>39,16%</t>
+          <t>38,68%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>35210</t>
+          <t>34795</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>48822</t>
+          <t>48435</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>62,04%</t>
+          <t>61,31%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>86,02%</t>
+          <t>85,34%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>27169</t>
+          <t>26511</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>46277</t>
+          <t>46231</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>49,66%</t>
+          <t>48,46%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>84,59%</t>
+          <t>84,5%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>67813</t>
+          <t>68357</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>91588</t>
+          <t>91353</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>60,84%</t>
+          <t>61,32%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>82,17%</t>
+          <t>81,96%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>60738</t>
+          <t>62196</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>99292</t>
+          <t>97889</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>28,83%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>83849</t>
+          <t>82978</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>135810</t>
+          <t>136476</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>38,34%</t>
+          <t>38,53%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>160456</t>
+          <t>160841</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>218460</t>
+          <t>220170</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>23,19%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>31,74%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>240213</t>
+          <t>241616</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>278767</t>
+          <t>277309</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>70,75%</t>
+          <t>71,17%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>82,11%</t>
+          <t>81,68%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>218405</t>
+          <t>217739</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>270366</t>
+          <t>271237</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>61,66%</t>
+          <t>61,47%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>76,33%</t>
+          <t>76,57%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>475260</t>
+          <t>473550</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>533264</t>
+          <t>532879</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>68,51%</t>
+          <t>68,26%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>76,87%</t>
+          <t>76,81%</t>
         </is>
       </c>
     </row>
